--- a/deliverables/function_list_v2/XD01-XD15_UR_Business_Logic_Summary.xlsx
+++ b/deliverables/function_list_v2/XD01-XD15_UR_Business_Logic_Summary.xlsx
@@ -886,7 +886,7 @@
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>1. All-or-nothing: 1 error = seluruh file ditolak.
-2. Flag A = part baru (Candidate), flag E = ubah; baris tanpa perubahan di-skip.
+2. Kolom upload: A = part baru (Candidate), E = ubah; baris tanpa perubahan di-skip.
 3. Max Case/Day tidak boleh &lt; total mapping.
 4. Result report + sheet Re-upload.</t>
         </is>
@@ -949,8 +949,9 @@
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>1. All-or-nothing.
-2. Part harus Active; destinasi ada di master H0125; 1 destinasi sekali per part.
-3. Total case_day per part ≤ Max Case/Day.
+2. Kolom upload A (destinasi baru) / E (sudah di-mapping).
+3. Part harus Active; destinasi ada di master H0125; 1 destinasi sekali per part.
+4. Total case_day per part ≤ Max Case/Day.
 4. Part berubah → replace seluruh mapping part + No Sync.</t>
         </is>
       </c>
@@ -2289,7 +2290,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>User Procurement upload file Excel (sheet "Upload") untuk Add (flag A) dan Edit (flag E) part.</t>
+          <t>User Procurement upload file Excel (sheet "Upload") untuk Add (upload = A) dan Edit (upload = E) part.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
@@ -2353,7 +2354,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Part ada di master; flag A belum terdaftar / flag E sudah terdaftar; tidak duplikat di file; min_mad bulat ≥ 0, pcs_case &amp; max_case_day bulat &gt; 0; status sesuai aturan (A kosong, E tidak boleh menjadi Candidate); Effective Start Date wajib selama Candidate dan ≥ hari ini; Max Case/Day ≥ total mapping.</t>
+          <t>upload = A atau E; part ada di master; A belum terdaftar / E sudah terdaftar; tidak duplikat di file; min_mad bulat ≥ 0, pcs_case &amp; max_case_day bulat &gt; 0; status sesuai aturan (A kosong, E tidak boleh menjadi Candidate); Effective Start Date wajib selama Candidate dan ≥ hari ini; Max Case/Day ≥ total mapping.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
@@ -2421,7 +2422,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Flag A insert status Candidate; flag E update kolom yang berubah (baris tanpa perubahan di-skip). Part tersimpan → SYNC_STATUS 0, LAST_SOURCE UPLOAD, history.</t>
+          <t>upload A insert status Candidate; upload E update kolom yang berubah (baris tanpa perubahan di-skip). Part tersimpan → SYNC_STATUS 0, LAST_SOURCE UPLOAD, history.</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -2525,7 +2526,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Cek file sama dengan XD02 (4 kolom). Part ada dan Active; destinasi ada di TB_M_H0125_DESTINATION; destinasi tidak duplikat per part; case_day bulat &gt; 0; total per part ≤ Max Case/Day. Baris placeholder kosong di-skip.</t>
+          <t>Cek file sama dengan XD02 (5 kolom). Kolom upload: A = destinasi baru untuk part, E = destinasi yang sudah di-mapping (Export mengisi E, A untuk placeholder). Part ada dan Active; destinasi ada di TB_M_H0125_DESTINATION; destinasi tidak duplikat per part; case_day bulat &gt; 0; total per part ≤ Max Case/Day. Baris placeholder kosong di-skip.</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">

--- a/deliverables/function_list_v2/XD01-XD15_UR_Business_Logic_Summary.xlsx
+++ b/deliverables/function_list_v2/XD01-XD15_UR_Business_Logic_Summary.xlsx
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>G-System / NSP</t>
+          <t>GTOPAS / NSP</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Mendaftarkan dan memelihara part crossdock (Min MAD, Pcs/Case, Max Case/Day, Effective Start Date) dan membagi Max Case/Day ke destinasi; mengirim master ke G-System / AP POLE lewat [Sync].</t>
+          <t>Mendaftarkan dan memelihara part crossdock (Min MAD, Pcs/Case, Max Case/Day, Effective Start Date) dan membagi Max Case/Day ke destinasi; mengirim master ke GTOPAS / AP POLE lewat [Sync].</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>IF Cross Dock Master to G-System</t>
+          <t>IF Cross Dock Master to GTOPAS</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Mengirim cross dock master (part + mapping destinasi) ke G-System supaya G-System tahu part / destinasi yang dilayani crossdock.</t>
+          <t>Mengirim cross dock master (part + mapping destinasi) ke GTOPAS supaya GTOPAS tahu part / destinasi yang dilayani crossdock.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>File IF / interface existing G-System, TB_R_CROSSDOCK_IF_RESULT, TB_M_PART_CANDIDATE</t>
+          <t>File IF / interface existing GTOPAS, TB_R_CROSSDOCK_IF_RESULT, TB_M_PART_CANDIDATE</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Membawa customer order crossdock H0253 (status 7 / 6 / 2) dari G-System ke NSP, mencatat perubahan status, dan menjaga ASN tetap konsisten dengan order.</t>
+          <t>Membawa customer order crossdock H0253 (status 7 / 6 / 2) dari GTOPAS ke NSP, mencatat perubahan status, dan menjaga ASN tetap konsisten dengan order.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Mengganti customer order yang di-cancel G-System setelah ASN Submit dengan customer order lain (part sama) tanpa mengubah ASN / case fisik.</t>
+          <t>Mengganti customer order yang di-cancel GTOPAS setelah ASN Submit dengan customer order lain (part sama) tanpa mengubah ASN / case fisik.</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Sync ke G-System &amp; AP POLE</t>
+          <t>Sync ke GTOPAS &amp; AP POLE</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>IF Cross Dock Master to G-System</t>
+          <t>IF Cross Dock Master to GTOPAS</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>G-System tahu part crossdock</t>
+          <t>GTOPAS tahu part crossdock</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>G-System perlu tahu part dan destinasi yang order-nya ditangani crossdock (order status 7) dan Case/Day per destinasi (asumsi, TBC).</t>
+          <t>GTOPAS perlu tahu part dan destinasi yang order-nya ditangani crossdock (order status 7) dan Case/Day per destinasi (asumsi, TBC).</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>IF Cross Dock Master to G-System</t>
+          <t>IF Cross Dock Master to GTOPAS</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Part dengan target G-System IF_STATUS 3 dan masih Active: PCS_CASE, MAX_CASE_DAY, semua destinasi + CASE_DAY periode berjalan (1 record per part × destinasi). Part Inactive dikirim CROSSDOCK_FLAG N tanpa destinasi.</t>
+          <t>Part dengan target GTOPAS IF_STATUS 3 dan masih Active: PCS_CASE, MAX_CASE_DAY, semua destinasi + CASE_DAY periode berjalan (1 record per part × destinasi). Part Inactive dikirim CROSSDOCK_FLAG N tanpa destinasi.</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>IF Cross Dock Master to G-System</t>
+          <t>IF Cross Dock Master to GTOPAS</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>G-System mengganti seluruh data cross dock part dengan isi kiriman (satu paket per part).</t>
+          <t>GTOPAS mengganti seluruh data cross dock part dengan isi kiriman (satu paket per part).</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>IF Cross Dock Master to G-System</t>
+          <t>IF Cross Dock Master to GTOPAS</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>IF Cross Dock Master to G-System</t>
+          <t>IF Cross Dock Master to GTOPAS</t>
         </is>
       </c>
       <c r="D41" s="17" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Keputusan 19-Oct: G-System memakai interface existing (bukan SFTP); nama / layout field G-System TBC.</t>
+          <t>Keputusan 19-Oct: GTOPAS memakai interface existing (bukan SFTP); nama / layout field GTOPAS TBC.</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Sama dengan XD06; Success hanya kalau G-System dan AP POLE dua-duanya terkirim.</t>
+          <t>Sama dengan XD06; Success hanya kalau GTOPAS dan AP POLE dua-duanya terkirim.</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Customer order crossdock dari G-System (H0253) harus ada di NSP setiap hari sebelum supplier membuat ASN, termasuk perubahan status received dan cancel.</t>
+          <t>Customer order crossdock dari GTOPAS (H0253) harus ada di NSP setiap hari sebelum supplier membuat ASN, termasuk perubahan status received dan cancel.</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>1 line di beberapa ASN dan di-receive terpisah: G-System memecah line (SERIAL_NO baru). Baris TB_R_INSTRUCTION ikut ke serial-nya; bagian received = ASN yang dikirim duluan. Bagian yang sudah di ASN tidak ditawarkan lagi. LOG7.</t>
+          <t>1 line di beberapa ASN dan di-receive terpisah: GTOPAS memecah line (SERIAL_NO baru). Baris TB_R_INSTRUCTION ikut ke serial-nya; bagian received = ASN yang dikirim duluan. Bagian yang sudah di ASN tidak ditawarkan lagi. LOG7.</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>D/S mengganti customer order yang di-cancel G-System setelah ASN Submit dengan order lain, supaya case fisik / ASN tidak berubah.</t>
+          <t>D/S mengganti customer order yang di-cancel GTOPAS setelah ASN Submit dengan order lain, supaya case fisik / ASN tidak berubah.</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Destinasi crossdock harus valid sesuai master H0125 G-System.</t>
+          <t>Destinasi crossdock harus valid sesuai master H0125 GTOPAS.</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Delete – insert TB_M_H0125_DESTINATION dari DB Surrounding; mingguan 21:30 setelah data G-System tersedia; retry 3x.</t>
+          <t>Delete – insert TB_M_H0125_DESTINATION dari DB Surrounding; mingguan 21:30 setelah data GTOPAS tersedia; retry 3x.</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
@@ -4522,7 +4522,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Tidak ada Cancel ASN di NSP; cancel order datang dari G-System (XD08) dan qty di ASN dipindah lewat XD11.</t>
+          <t>Tidak ada Cancel ASN di NSP; cancel order datang dari GTOPAS (XD08) dan qty di ASN dipindah lewat XD11.</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Kalau di-receive terpisah, G-System memecah line di H0253 (SERIAL_NO baru); tiap bagian tetap terhubung ke ASN-nya (asumsi urutan receive = urutan ASN, TBC).</t>
+          <t>Kalau di-receive terpisah, GTOPAS memecah line di H0253 (SERIAL_NO baru); tiap bagian tetap terhubung ke ASN-nya (asumsi urutan receive = urutan ASN, TBC).</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Urutan receive di G-System = urutan ASN? Kalau tidak, G-System perlu kirim ASN No yang di-receive.</t>
+          <t>Urutan receive di GTOPAS = urutan ASN? Kalau tidak, GTOPAS perlu kirim ASN No yang di-receive.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>G-System</t>
+          <t>GTOPAS</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Layout / nama field target G-System dan AP POLE; detail SFTP AP POLE dan acknowledge.</t>
+          <t>Layout / nama field target GTOPAS dan AP POLE; detail SFTP AP POLE dan acknowledge.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>G-System / AP POLE</t>
+          <t>GTOPAS / AP POLE</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">

--- a/deliverables/function_list_v2/XD01-XD15_UR_Business_Logic_Summary.xlsx
+++ b/deliverables/function_list_v2/XD01-XD15_UR_Business_Logic_Summary.xlsx
@@ -1862,17 +1862,13 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Filter Part No, Status (All / Candidate / Active / Inactive), Sort; diterapkan saat [Search]. 25/50/100 baris per halaman. Counter "N parts · M incomplete mappings".</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Incomplete mapping = part tanpa destinasi atau total Case/Day ≠ Max Case/Day (bar biru).</t>
-        </is>
-      </c>
+          <t>Filter Part No, Status (All / Candidate / Active / Inactive), Sort; diterapkan saat [Search]. 25/50/100 baris per halaman. Counter "N parts". Kelengkapan mapping dipantau D/S di tab Mapping per Destination (FB-024).</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>TB_M_PART_CANDIDATE, TB_M_PART_CANDIDATE_DEST</t>
+          <t>TB_M_PART_CANDIDATE</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2006,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Max Case/Day tidak boleh lebih kecil dari total Case/Day yang sudah di-mapping periode berjalan (MSG14, Save disabled). Kurangi mapping dulu.</t>
+          <t>Max Case/Day tidak boleh lebih kecil dari total Case/Day yang sudah di-mapping periode berjalan (MSG14, Save disabled). Modal Edit menampilkan "Mapped Case/Day (current period)" sebagai batas bawah (FB-025). Kurangi mapping dulu.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
